--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92552617138</v>
+        <v>46157.93105618639</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105618639</v>
+        <v>46157.93131398474</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93131398474</v>
+        <v>46157.93379419578</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93379419578</v>
+        <v>46157.93689696381</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93689696381</v>
+        <v>46158.28202817024</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28202817024</v>
+        <v>46158.29732837628</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29732837628</v>
+        <v>46158.29802053961</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29802053961</v>
+        <v>46158.33366405927</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33366405927</v>
+        <v>46158.37218280611</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Заявки/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37218280611</v>
+        <v>46158.37273396378</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
